--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 25.0%  (2W / 6L of 8 evaluated)</t>
+          <t>Win Rate: 12.5%  (1W / 7L of 8 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>225.5</v>
       </c>
       <c r="D9" t="n">
         <v>193</v>
@@ -721,10 +721,10 @@
         <v>228</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-14.6</v>
+        <v>-14.41</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="D10" t="n">
         <v>980</v>
@@ -763,14 +763,14 @@
         <v>980</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="D12" t="n">
         <v>1000</v>
@@ -847,10 +847,10 @@
         <v>1025</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.96</v>
+        <v>-2.91</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 40.9%  (9W / 13L of 22 evaluated, 1 pending)</t>
+          <t>Win Rate: 27.3%  (6W / 16L of 22 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c r="D5" t="n">
         <v>715</v>
@@ -981,10 +981,10 @@
         <v>740</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16.54</v>
+        <v>21.31</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>12.6</v>
+        <v>17.21</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D6" t="n">
         <v>274</v>
@@ -1023,10 +1023,10 @@
         <v>280</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.14</v>
+        <v>-0.72</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>288.75</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
         <v>302.67</v>
@@ -1065,14 +1065,14 @@
         <v>307.89</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.63</v>
+        <v>-7.82</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6100</v>
+        <v>5900</v>
       </c>
       <c r="D9" t="n">
         <v>5825</v>
@@ -1139,10 +1139,10 @@
         <v>6100</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.51</v>
+        <v>-1.27</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="D11" t="n">
         <v>1165</v>
@@ -1223,10 +1223,10 @@
         <v>1375</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-14.96</v>
+        <v>-14.65</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="D12" t="n">
         <v>434</v>
@@ -1265,14 +1265,14 @@
         <v>442</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.31</v>
+        <v>-7.92</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-9.58</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D14" t="n">
         <v>258</v>
@@ -1349,10 +1349,10 @@
         <v>258</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>24.04</v>
+        <v>32.99</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>24.04</v>
+        <v>32.99</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
         <v>65</v>
@@ -1391,10 +1391,10 @@
         <v>73</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.39</v>
+        <v>2.82</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-9.720000000000001</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>226</v>
+        <v>225.5</v>
       </c>
       <c r="D17" t="n">
         <v>193</v>
@@ -1475,10 +1475,10 @@
         <v>228</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-14.6</v>
+        <v>-14.41</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D18" t="n">
         <v>91</v>
@@ -1517,10 +1517,10 @@
         <v>121</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>32.97</v>
+        <v>16.35</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D19" t="n">
         <v>266</v>
@@ -1559,10 +1559,10 @@
         <v>296</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-10.14</v>
+        <v>-5</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
         <v>156</v>
@@ -1601,10 +1601,10 @@
         <v>157</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.37</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.7</v>
+        <v>9.09</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D21" t="n">
         <v>348</v>
@@ -1643,10 +1643,10 @@
         <v>362</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.02</v>
+        <v>3.43</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>700</v>
+        <v>655</v>
       </c>
       <c r="D22" t="n">
         <v>750</v>
@@ -1685,10 +1685,10 @@
         <v>785</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>12.14</v>
+        <v>19.85</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>7.14</v>
+        <v>14.5</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D23" t="n">
         <v>103</v>
@@ -1727,10 +1727,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>20</v>
+        <v>14.05</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-10.43</v>
+        <v>-14.88</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="D24" t="n">
         <v>725</v>
@@ -1769,14 +1769,14 @@
         <v>770</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.94</v>
+        <v>6.21</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4150</v>
+        <v>4160</v>
       </c>
       <c r="D25" t="n">
         <v>4000</v>
@@ -1811,10 +1811,10 @@
         <v>4180</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.61</v>
+        <v>-3.85</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="D26" t="n">
         <v>1000</v>
@@ -1853,10 +1853,10 @@
         <v>1025</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.96</v>
+        <v>-2.91</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D27" t="n">
         <v>216</v>
@@ -1895,10 +1895,10 @@
         <v>218</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.81</v>
+        <v>2.83</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.86</v>
+        <v>1.89</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-06-03</t>
+          <t>Swing — Review sesi market 2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 12.5%  (1W / 7L of 8 evaluated)</t>
+          <t>Win Rate: 15.4%  (2W / 11L of 13 evaluated)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DMAS.JK</t>
+          <t>ADES.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>156</v>
+        <v>22225</v>
       </c>
       <c r="D5" t="n">
-        <v>153</v>
+        <v>21950</v>
       </c>
       <c r="E5" t="n">
-        <v>156</v>
+        <v>22400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.24</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>DMAS.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1115</v>
+        <v>159</v>
       </c>
       <c r="D6" t="n">
-        <v>1115</v>
+        <v>156</v>
       </c>
       <c r="E6" t="n">
-        <v>1120</v>
+        <v>161</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.45</v>
+        <v>1.26</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -628,19 +628,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2620</v>
+        <v>9900</v>
       </c>
       <c r="D7" t="n">
-        <v>2450</v>
+        <v>9600</v>
       </c>
       <c r="E7" t="n">
-        <v>2620</v>
+        <v>10900</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.49</v>
+        <v>-3.03</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MGLV.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8100</v>
+        <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>8175</v>
+        <v>1175</v>
       </c>
       <c r="E8" t="n">
-        <v>8900</v>
+        <v>1220</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-2.49</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>225.5</v>
+        <v>1485</v>
       </c>
       <c r="D9" t="n">
-        <v>193</v>
+        <v>1495</v>
       </c>
       <c r="E9" t="n">
-        <v>228</v>
+        <v>1500</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-14.41</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.67</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DRMA.JK</t>
+          <t>PANS.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>980</v>
+        <v>1740</v>
       </c>
       <c r="D10" t="n">
-        <v>980</v>
+        <v>1725</v>
       </c>
       <c r="E10" t="n">
-        <v>980</v>
+        <v>1740</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -787,28 +787,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>510</v>
+        <v>2850</v>
       </c>
       <c r="D11" t="n">
-        <v>505</v>
+        <v>2620</v>
       </c>
       <c r="E11" t="n">
-        <v>515</v>
+        <v>2850</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.98</v>
+        <v>-8.07</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -829,40 +829,250 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>KJEN.JK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>181</v>
+      </c>
+      <c r="D12" t="n">
+        <v>154</v>
+      </c>
+      <c r="E12" t="n">
+        <v>165</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>-8.84</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-14.92</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KEJU.JK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>625</v>
+      </c>
+      <c r="D13" t="n">
+        <v>615</v>
+      </c>
+      <c r="E13" t="n">
+        <v>635</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UVCR.JK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>242</v>
+      </c>
+      <c r="D14" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>241.46</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HATM.JK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>382</v>
+      </c>
+      <c r="D15" t="n">
+        <v>350</v>
+      </c>
+      <c r="E15" t="n">
+        <v>382</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>VISI.JK</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BREAKOUT</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>905</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KETR.JK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1030</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1025</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="C17" t="n">
+        <v>660</v>
+      </c>
+      <c r="D17" t="n">
+        <v>565</v>
+      </c>
+      <c r="E17" t="n">
+        <v>670</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-14.39</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -879,7 +1089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -897,14 +1107,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-06-03</t>
+          <t>Scalping — Review sesi market 2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 27.3%  (6W / 16L of 22 evaluated, 1 pending)</t>
+          <t>Win Rate: 24.4%  (10W / 31L of 41 evaluated)</t>
         </is>
       </c>
     </row>
@@ -963,7 +1173,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>ABDA.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -972,28 +1182,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>610</v>
+        <v>3500</v>
       </c>
       <c r="D5" t="n">
-        <v>715</v>
+        <v>3120</v>
       </c>
       <c r="E5" t="n">
-        <v>740</v>
+        <v>3400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>21.31</v>
+        <v>-2.86</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-10.86</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1005,7 +1215,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMIN.JK</t>
+          <t>ALKA.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,19 +1224,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>276</v>
+        <v>685</v>
       </c>
       <c r="D6" t="n">
-        <v>274</v>
+        <v>610</v>
       </c>
       <c r="E6" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.45</v>
+        <v>2.19</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.72</v>
+        <v>-10.95</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -1035,7 +1245,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1047,7 +1257,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APLI.JK</t>
+          <t>AMIN.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1056,28 +1266,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="D7" t="n">
-        <v>302.67</v>
+        <v>276</v>
       </c>
       <c r="E7" t="n">
-        <v>307.89</v>
+        <v>278</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.82</v>
+        <v>1.46</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.73</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1089,7 +1299,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>AMRT.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1098,30 +1308,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v/>
+        <v>1380</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>1350</v>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>1390</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v/>
+        <v>0.72</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v/>
+        <v>-2.17</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>APLI.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1130,28 +1350,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5900</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>5825</v>
+        <v>334</v>
       </c>
       <c r="E9" t="n">
-        <v>6100</v>
+        <v>356</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.45</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1163,7 +1383,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1172,19 +1392,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>114</v>
+        <v>2760</v>
       </c>
       <c r="D10" t="n">
-        <v>102</v>
+        <v>2350</v>
       </c>
       <c r="E10" t="n">
-        <v>116</v>
+        <v>3200</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.75</v>
+        <v>15.94</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-10.53</v>
+        <v>-14.86</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1193,7 +1413,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1205,7 +1425,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>ASDM.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1214,19 +1434,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1365</v>
+        <v>545</v>
       </c>
       <c r="D11" t="n">
-        <v>1165</v>
+        <v>530</v>
       </c>
       <c r="E11" t="n">
-        <v>1375</v>
+        <v>550</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-14.65</v>
+        <v>-2.75</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1235,7 +1455,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1247,7 +1467,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TIRT.JK</t>
+          <t>BRPT.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1256,19 +1476,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>480</v>
+        <v>1930</v>
       </c>
       <c r="D12" t="n">
-        <v>434</v>
+        <v>1765</v>
       </c>
       <c r="E12" t="n">
-        <v>442</v>
+        <v>1925</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-7.92</v>
+        <v>-0.26</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-9.58</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -1277,7 +1497,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1289,7 +1509,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WEHA.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1298,19 +1518,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>167</v>
+        <v>6000</v>
       </c>
       <c r="D13" t="n">
-        <v>142</v>
+        <v>5900</v>
       </c>
       <c r="E13" t="n">
-        <v>182</v>
+        <v>6150</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.98</v>
+        <v>2.5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-14.97</v>
+        <v>-1.67</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1319,7 +1539,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1331,7 +1551,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>DNET.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1340,28 +1560,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>194</v>
+        <v>9900</v>
       </c>
       <c r="D14" t="n">
-        <v>258</v>
+        <v>9600</v>
       </c>
       <c r="E14" t="n">
-        <v>258</v>
+        <v>10900</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>32.99</v>
+        <v>10.1</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-3.03</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1373,7 +1593,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NPGF.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1382,19 +1602,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>1130</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>1115</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>1135</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.82</v>
+        <v>0.44</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-8.449999999999999</v>
+        <v>-1.33</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1403,7 +1623,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1415,7 +1635,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MGLV.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1424,19 +1644,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8100</v>
+        <v>1100</v>
       </c>
       <c r="D16" t="n">
-        <v>8175</v>
+        <v>1365</v>
       </c>
       <c r="E16" t="n">
-        <v>8900</v>
+        <v>1375</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>25</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.93</v>
+        <v>24.09</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -1445,7 +1665,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,7 +1677,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>PTRO.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1466,19 +1686,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>225.5</v>
+        <v>4800</v>
       </c>
       <c r="D17" t="n">
-        <v>193</v>
+        <v>4110</v>
       </c>
       <c r="E17" t="n">
-        <v>228</v>
+        <v>4720</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.11</v>
+        <v>-1.67</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-14.41</v>
+        <v>-14.37</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1487,7 +1707,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1499,7 +1719,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>TIRT.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,19 +1728,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>104</v>
+        <v>505</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>480</v>
       </c>
       <c r="E18" t="n">
-        <v>121</v>
+        <v>550</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>16.35</v>
+        <v>8.91</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-12.5</v>
+        <v>-4.95</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1529,7 +1749,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1541,7 +1761,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1550,19 +1770,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>280</v>
+        <v>2850</v>
       </c>
       <c r="D19" t="n">
-        <v>266</v>
+        <v>2620</v>
       </c>
       <c r="E19" t="n">
-        <v>296</v>
+        <v>2850</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5</v>
+        <v>-8.07</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1571,7 +1791,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1583,7 +1803,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WGSH.JK</t>
+          <t>INPS.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1592,28 +1812,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>143</v>
+        <v>750</v>
       </c>
       <c r="D20" t="n">
-        <v>156</v>
+        <v>750</v>
       </c>
       <c r="E20" t="n">
-        <v>157</v>
+        <v>805</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1625,7 +1845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1634,19 +1854,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c r="D21" t="n">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="E21" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.57</v>
+        <v>-11.49</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1655,7 +1875,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1667,7 +1887,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1676,28 +1896,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>655</v>
+        <v>181</v>
       </c>
       <c r="D22" t="n">
-        <v>750</v>
+        <v>154</v>
       </c>
       <c r="E22" t="n">
-        <v>785</v>
+        <v>165</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>19.85</v>
+        <v>-8.84</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-14.92</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1709,7 +1929,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BEER.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1718,28 +1938,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="D23" t="n">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="E23" t="n">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>14.05</v>
+        <v>28.09</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-14.88</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>8.99</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1751,7 +1971,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>KEJU.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1760,19 +1980,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>725</v>
+        <v>625</v>
       </c>
       <c r="D24" t="n">
-        <v>725</v>
+        <v>615</v>
       </c>
       <c r="E24" t="n">
-        <v>770</v>
+        <v>635</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.21</v>
+        <v>1.6</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -1781,7 +2001,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1793,7 +2013,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>NPGF.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1802,28 +2022,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4160</v>
+        <v>70</v>
       </c>
       <c r="D25" t="n">
-        <v>4000</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
-        <v>4180</v>
+        <v>75</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.48</v>
+        <v>7.14</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.43</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1835,7 +2055,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>FLMC.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1844,19 +2064,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1030</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>1000</v>
+        <v>154</v>
       </c>
       <c r="E26" t="n">
-        <v>1025</v>
+        <v>164</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.91</v>
+        <v>-6.1</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1865,7 +2085,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1877,40 +2097,796 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>UVCR.JK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>242</v>
+      </c>
+      <c r="D27" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>241.46</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KUAS.JK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>122</v>
+      </c>
+      <c r="D28" t="n">
+        <v>104</v>
+      </c>
+      <c r="E28" t="n">
+        <v>143</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BOBA.JK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>282</v>
+      </c>
+      <c r="D29" t="n">
+        <v>280</v>
+      </c>
+      <c r="E29" t="n">
+        <v>332.87</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CMRY.JK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4790</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4540</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4790</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WGSH.JK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>137</v>
+      </c>
+      <c r="D31" t="n">
+        <v>143</v>
+      </c>
+      <c r="E31" t="n">
+        <v>145</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MTMH.JK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1045</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IBOS.JK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>101</v>
+      </c>
+      <c r="D33" t="n">
+        <v>93</v>
+      </c>
+      <c r="E33" t="n">
+        <v>102</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HATM.JK</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>382</v>
+      </c>
+      <c r="D34" t="n">
+        <v>350</v>
+      </c>
+      <c r="E34" t="n">
+        <v>382</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KKES.JK</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+      <c r="D35" t="n">
+        <v>45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MMIX.JK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>525</v>
+      </c>
+      <c r="D36" t="n">
+        <v>655</v>
+      </c>
+      <c r="E36" t="n">
+        <v>655</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BEER.JK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>112</v>
+      </c>
+      <c r="D37" t="n">
+        <v>121</v>
+      </c>
+      <c r="E37" t="n">
+        <v>128</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CUAN.JK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>785</v>
+      </c>
+      <c r="D38" t="n">
+        <v>725</v>
+      </c>
+      <c r="E38" t="n">
+        <v>855</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AMMN.JK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3890</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3310</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3900</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-14.91</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BREN.JK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4120</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4220</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UDNG.JK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1435</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1295</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1465</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VISI.JK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>905</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AWAN.JK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>154</v>
+      </c>
+      <c r="D43" t="n">
+        <v>136</v>
+      </c>
+      <c r="E43" t="n">
+        <v>154</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-11.69</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KETR.JK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>660</v>
+      </c>
+      <c r="D44" t="n">
+        <v>565</v>
+      </c>
+      <c r="E44" t="n">
+        <v>670</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-14.39</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>ADMG.JK</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>214</v>
+      </c>
+      <c r="D45" t="n">
         <v>212</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E45" t="n">
         <v>216</v>
       </c>
-      <c r="E27" t="n">
-        <v>218</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F45" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -673,16 +673,16 @@
         <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>1175</v>
+        <v>1092.54</v>
       </c>
       <c r="E8" t="n">
-        <v>1220</v>
+        <v>1134.39</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.24</v>
+        <v>-5.86</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.49</v>
+        <v>-9.33</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 24.4%  (10W / 31L of 41 evaluated)</t>
+          <t>Win Rate: 22.0%  (9W / 32L of 41 evaluated)</t>
         </is>
       </c>
     </row>
@@ -1353,20 +1353,20 @@
         <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>290.49</v>
       </c>
       <c r="E9" t="n">
-        <v>356</v>
+        <v>309.63</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>-5.02</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-10.89</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1605,16 +1605,16 @@
         <v>1130</v>
       </c>
       <c r="D15" t="n">
-        <v>1115</v>
+        <v>937.85</v>
       </c>
       <c r="E15" t="n">
-        <v>1135</v>
+        <v>954.67</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.44</v>
+        <v>-15.52</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.33</v>
+        <v>-17</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -673,16 +673,16 @@
         <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>1092.54</v>
+        <v>1175</v>
       </c>
       <c r="E8" t="n">
-        <v>1134.39</v>
+        <v>1220</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.86</v>
+        <v>1.24</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-9.33</v>
+        <v>-2.49</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 22.0%  (9W / 32L of 41 evaluated)</t>
+          <t>Win Rate: 24.4%  (10W / 31L of 41 evaluated)</t>
         </is>
       </c>
     </row>
@@ -1353,20 +1353,20 @@
         <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>290.49</v>
+        <v>334</v>
       </c>
       <c r="E9" t="n">
-        <v>309.63</v>
+        <v>356</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.02</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.89</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.45</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1605,16 +1605,16 @@
         <v>1130</v>
       </c>
       <c r="D15" t="n">
-        <v>937.85</v>
+        <v>1115</v>
       </c>
       <c r="E15" t="n">
-        <v>954.67</v>
+        <v>1135</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-15.52</v>
+        <v>0.44</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-17</v>
+        <v>-1.33</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -673,16 +673,16 @@
         <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>1175</v>
+        <v>1092.54</v>
       </c>
       <c r="E8" t="n">
-        <v>1220</v>
+        <v>1134.39</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.24</v>
+        <v>-5.86</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.49</v>
+        <v>-9.33</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 24.4%  (10W / 31L of 41 evaluated)</t>
+          <t>Win Rate: 22.0%  (9W / 32L of 41 evaluated)</t>
         </is>
       </c>
     </row>
@@ -1311,16 +1311,16 @@
         <v>1380</v>
       </c>
       <c r="D8" t="n">
-        <v>1350</v>
+        <v>1309.25</v>
       </c>
       <c r="E8" t="n">
-        <v>1390</v>
+        <v>1348.05</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.72</v>
+        <v>-2.32</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.17</v>
+        <v>-5.13</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1353,20 +1353,20 @@
         <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>290.49</v>
       </c>
       <c r="E9" t="n">
-        <v>356</v>
+        <v>309.63</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>-5.02</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-10.89</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1605,16 +1605,16 @@
         <v>1130</v>
       </c>
       <c r="D15" t="n">
-        <v>1115</v>
+        <v>937.85</v>
       </c>
       <c r="E15" t="n">
-        <v>1135</v>
+        <v>954.67</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.44</v>
+        <v>-15.52</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.33</v>
+        <v>-17</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -602,15 +613,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -644,15 +660,20 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>-9.33</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-8.07</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-14.92</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -896,15 +942,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>-6.82</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -978,17 +1034,22 @@
       <c r="G15" s="4" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1020,17 +1081,22 @@
       <c r="G16" s="4" t="n">
         <v>13.81</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1064,15 +1130,20 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1089,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1099,9 +1170,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,7 +1203,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1156,15 +1228,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G5" s="4" t="n">
         <v>-10.86</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1240,15 +1322,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G7" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1322,17 +1414,22 @@
       <c r="G8" s="4" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G9" s="4" t="n">
         <v>-10.89</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1408,15 +1510,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,15 +1557,20 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1490,17 +1602,22 @@
       <c r="G12" s="4" t="n">
         <v>-8.550000000000001</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1534,15 +1651,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1576,15 +1698,20 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1616,17 +1743,22 @@
       <c r="G15" s="4" t="n">
         <v>-17</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1658,17 +1790,22 @@
       <c r="G16" s="4" t="n">
         <v>24.09</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1700,17 +1837,22 @@
       <c r="G17" s="4" t="n">
         <v>-14.37</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1744,15 +1886,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1784,17 +1931,22 @@
       <c r="G19" s="4" t="n">
         <v>-8.07</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1828,15 +1980,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1868,17 +2025,22 @@
       <c r="G21" s="4" t="n">
         <v>-11.49</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1910,17 +2072,22 @@
       <c r="G22" s="4" t="n">
         <v>-14.92</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1952,17 +2119,22 @@
       <c r="G23" s="4" t="n">
         <v>8.99</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1996,15 +2168,20 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2036,17 +2213,22 @@
       <c r="G25" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2078,17 +2260,22 @@
       <c r="G26" s="4" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2120,17 +2307,22 @@
       <c r="G27" s="4" t="n">
         <v>-6.82</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2164,15 +2356,20 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2206,15 +2403,20 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2246,17 +2448,22 @@
       <c r="G30" s="4" t="n">
         <v>-5.22</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G31" s="4" t="n">
         <v>4.38</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2330,17 +2542,22 @@
       <c r="G32" s="4" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2374,15 +2591,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2414,17 +2636,22 @@
       <c r="G34" s="4" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2456,17 +2683,22 @@
       <c r="G35" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2498,17 +2730,22 @@
       <c r="G36" s="4" t="n">
         <v>24.76</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2540,17 +2777,22 @@
       <c r="G37" s="4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2584,15 +2826,20 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2626,15 +2873,20 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2666,17 +2918,22 @@
       <c r="G40" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2710,15 +2967,20 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2750,17 +3012,22 @@
       <c r="G42" s="4" t="n">
         <v>13.81</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2792,17 +3059,22 @@
       <c r="G43" s="4" t="n">
         <v>-11.69</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2836,15 +3108,20 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2878,15 +3155,20 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-03.xlsx
+++ b/data/performance/daily/signal_list_2026-06-03.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>22225</v>
       </c>
       <c r="D5" t="n">
+        <v>22225</v>
+      </c>
+      <c r="E5" t="n">
         <v>21950</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>22400</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-1.24</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>159</v>
       </c>
       <c r="D6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E6" t="n">
         <v>156</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>161</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.89</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>9900</v>
       </c>
       <c r="D7" t="n">
+        <v>10300</v>
+      </c>
+      <c r="E7" t="n">
         <v>9600</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>10900</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>10.1</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-3.03</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>1205</v>
       </c>
       <c r="D8" t="n">
+        <v>1220</v>
+      </c>
+      <c r="E8" t="n">
         <v>1092.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1134.39</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>-5.86</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-9.33</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -744,30 +762,33 @@
         <v>1495</v>
       </c>
       <c r="E9" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F9" t="n">
         <v>1500</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>1740</v>
       </c>
       <c r="D10" t="n">
+        <v>1740</v>
+      </c>
+      <c r="E10" t="n">
         <v>1725</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1740</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>2850</v>
       </c>
       <c r="D11" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E11" t="n">
         <v>2620</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>2850</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-8.07</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>181</v>
       </c>
       <c r="D12" t="n">
+        <v>164</v>
+      </c>
+      <c r="E12" t="n">
         <v>154</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>165</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>-8.84</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-14.92</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>625</v>
       </c>
       <c r="D13" t="n">
+        <v>625</v>
+      </c>
+      <c r="E13" t="n">
         <v>615</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>635</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-1.6</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>242</v>
       </c>
       <c r="D14" t="n">
+        <v>241.46</v>
+      </c>
+      <c r="E14" t="n">
         <v>225.5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>241.46</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>-0.22</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-6.82</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>382</v>
       </c>
       <c r="D15" t="n">
+        <v>382</v>
+      </c>
+      <c r="E15" t="n">
         <v>350</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>382</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>905</v>
       </c>
       <c r="D16" t="n">
+        <v>920</v>
+      </c>
+      <c r="E16" t="n">
         <v>1030</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1130</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>24.86</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>13.81</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>660</v>
       </c>
       <c r="D17" t="n">
+        <v>670</v>
+      </c>
+      <c r="E17" t="n">
         <v>565</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>670</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-14.39</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1160,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1168,12 +1213,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1203,45 +1249,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>3500</v>
       </c>
       <c r="D5" t="n">
+        <v>3150</v>
+      </c>
+      <c r="E5" t="n">
         <v>3120</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3400</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>-2.86</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-10.86</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>685</v>
       </c>
       <c r="D6" t="n">
+        <v>690</v>
+      </c>
+      <c r="E6" t="n">
         <v>610</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>700</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-10.95</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>274</v>
       </c>
       <c r="D7" t="n">
+        <v>272</v>
+      </c>
+      <c r="E7" t="n">
         <v>276</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>278</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>1380</v>
       </c>
       <c r="D8" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E8" t="n">
         <v>1309.25</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1348.05</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>-2.32</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>326</v>
       </c>
       <c r="D9" t="n">
+        <v>348</v>
+      </c>
+      <c r="E9" t="n">
         <v>290.49</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>309.63</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>-5.02</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-10.89</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>2760</v>
       </c>
       <c r="D10" t="n">
+        <v>2760</v>
+      </c>
+      <c r="E10" t="n">
         <v>2350</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>3200</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>15.94</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-14.86</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>545</v>
       </c>
       <c r="D11" t="n">
+        <v>550</v>
+      </c>
+      <c r="E11" t="n">
         <v>530</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>550</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-2.75</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>1930</v>
       </c>
       <c r="D12" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E12" t="n">
         <v>1765</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1925</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>-0.26</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-8.550000000000001</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>6000</v>
       </c>
       <c r="D13" t="n">
+        <v>6150</v>
+      </c>
+      <c r="E13" t="n">
         <v>5900</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>6150</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>9900</v>
       </c>
       <c r="D14" t="n">
+        <v>10300</v>
+      </c>
+      <c r="E14" t="n">
         <v>9600</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>10900</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>10.1</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-3.03</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>1130</v>
       </c>
       <c r="D15" t="n">
+        <v>1130</v>
+      </c>
+      <c r="E15" t="n">
         <v>937.85</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>954.67</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>-15.52</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-17</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>1100</v>
       </c>
       <c r="D16" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E16" t="n">
         <v>1365</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1375</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>24.09</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>4800</v>
       </c>
       <c r="D17" t="n">
+        <v>4670</v>
+      </c>
+      <c r="E17" t="n">
         <v>4110</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>4720</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-14.37</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>505</v>
       </c>
       <c r="D18" t="n">
+        <v>550</v>
+      </c>
+      <c r="E18" t="n">
         <v>480</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>550</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>8.91</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>2850</v>
       </c>
       <c r="D19" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E19" t="n">
         <v>2620</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>2850</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-8.07</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>750</v>
       </c>
       <c r="D20" t="n">
+        <v>805</v>
+      </c>
+      <c r="E20" t="n">
         <v>750</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>805</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>7.33</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>87</v>
       </c>
       <c r="D21" t="n">
+        <v>86</v>
+      </c>
+      <c r="E21" t="n">
         <v>77</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>87</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-11.49</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>181</v>
       </c>
       <c r="D22" t="n">
+        <v>164</v>
+      </c>
+      <c r="E22" t="n">
         <v>154</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>165</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>-8.84</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-14.92</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>178</v>
       </c>
       <c r="D23" t="n">
+        <v>177</v>
+      </c>
+      <c r="E23" t="n">
         <v>194</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>228</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>28.09</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>8.99</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>625</v>
       </c>
       <c r="D24" t="n">
+        <v>625</v>
+      </c>
+      <c r="E24" t="n">
         <v>615</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>635</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-1.6</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>70</v>
       </c>
       <c r="D25" t="n">
+        <v>70</v>
+      </c>
+      <c r="E25" t="n">
         <v>71</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>75</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
+        <v>163</v>
+      </c>
+      <c r="E26" t="n">
         <v>154</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>164</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>242</v>
       </c>
       <c r="D27" t="n">
+        <v>241.46</v>
+      </c>
+      <c r="E27" t="n">
         <v>225.5</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>241.46</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>-0.22</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-6.82</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>122</v>
       </c>
       <c r="D28" t="n">
+        <v>132</v>
+      </c>
+      <c r="E28" t="n">
         <v>104</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>143</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>17.21</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-14.75</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>282</v>
       </c>
       <c r="D29" t="n">
+        <v>299.58</v>
+      </c>
+      <c r="E29" t="n">
         <v>280</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>332.87</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>18.04</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>4790</v>
       </c>
       <c r="D30" t="n">
+        <v>4790</v>
+      </c>
+      <c r="E30" t="n">
         <v>4540</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>4790</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-5.22</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>137</v>
       </c>
       <c r="D31" t="n">
+        <v>138</v>
+      </c>
+      <c r="E31" t="n">
         <v>143</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>145</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>5.84</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>4.38</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>1050</v>
       </c>
       <c r="D32" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E32" t="n">
         <v>1030</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>1045</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>-0.48</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>101</v>
       </c>
       <c r="D33" t="n">
+        <v>102</v>
+      </c>
+      <c r="E33" t="n">
         <v>93</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>102</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-7.92</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>382</v>
       </c>
       <c r="D34" t="n">
+        <v>382</v>
+      </c>
+      <c r="E34" t="n">
         <v>350</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>382</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>50</v>
       </c>
       <c r="D35" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" t="n">
         <v>45</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>50</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>525</v>
       </c>
       <c r="D36" t="n">
-        <v>655</v>
+        <v>525</v>
       </c>
       <c r="E36" t="n">
         <v>655</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>24.76</v>
+      <c r="F36" t="n">
+        <v>655</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>24.76</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H36" s="4" t="n">
+        <v>24.76</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>112</v>
       </c>
       <c r="D37" t="n">
+        <v>112</v>
+      </c>
+      <c r="E37" t="n">
         <v>121</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>128</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>14.29</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>785</v>
       </c>
       <c r="D38" t="n">
+        <v>855</v>
+      </c>
+      <c r="E38" t="n">
         <v>725</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>855</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>8.92</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-7.64</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>3890</v>
       </c>
       <c r="D39" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E39" t="n">
         <v>3310</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>3900</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>-14.91</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>4120</v>
       </c>
       <c r="D40" t="n">
+        <v>4120</v>
+      </c>
+      <c r="E40" t="n">
         <v>4160</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>4220</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>2.43</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>1435</v>
       </c>
       <c r="D41" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E41" t="n">
         <v>1295</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>1465</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-9.76</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>905</v>
       </c>
       <c r="D42" t="n">
+        <v>920</v>
+      </c>
+      <c r="E42" t="n">
         <v>1030</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1130</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>24.86</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>13.81</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>154</v>
       </c>
       <c r="D43" t="n">
+        <v>154</v>
+      </c>
+      <c r="E43" t="n">
         <v>136</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>154</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-11.69</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>660</v>
       </c>
       <c r="D44" t="n">
+        <v>670</v>
+      </c>
+      <c r="E44" t="n">
         <v>565</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>670</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-14.39</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>214</v>
       </c>
       <c r="D45" t="n">
+        <v>214</v>
+      </c>
+      <c r="E45" t="n">
         <v>212</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>216</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-0.93</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
